--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוסף עבאדי - רגעים של אושר</v>
+        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409439&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409444&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוסף עבאדי - רגעים של אושר</v>
+        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהונתן ישראל - אבא תודה</v>
+        <v>פרחי ירושלים - סומלילנד</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409438&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409443&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהונתן ישראל - אבא תודה</v>
+        <v>פרחי ירושלים - סומלילנד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל יטיב - תודה</v>
+        <v>מתנאל סבח - שדרות דוממת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409437&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409442&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-01</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל יטיב - תודה</v>
+        <v>מתנאל סבח - שדרות דוממת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409436&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409441&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-01</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
+        <v>אורי זר - חוזר לילדות</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409435&amp;sid=755baf5a9e427242a5603345f7826207</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409440&amp;sid=c5c30978038848a81687864b9fc464f8</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-01</v>
@@ -621,164 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>בניה ברבי - מהודו להודו</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בן שוקרון - יותר שמיים</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409434&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בן שוקרון - יותר שמיים</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אסף בר נתן - אם זה שורף</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409433&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אסף בר נתן - אם זה שורף</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>איציק וינגרטן - רק מנגינות</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409432&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>איציק וינגרטן - רק מנגינות</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אביחי פרץ - מי לי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409431&amp;sid=755baf5a9e427242a5603345f7826207</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אביחי פרץ - מי לי</v>
+        <v>אורי זר - חוזר לילדות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
+        <v>ששון שאולוב - חשבונות שמיים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409444&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409446&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - שיר היובל 50 שנה</v>
+        <v>ששון שאולוב - חשבונות שמיים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>פרחי ירושלים - סומלילנד</v>
+        <v>רפאל שילוני - מחכה לך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409443&amp;sid=c5c30978038848a81687864b9fc464f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409445&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>
@@ -507,126 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>פרחי ירושלים - סומלילנד</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מתנאל סבח - שדרות דוממת</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409442&amp;sid=c5c30978038848a81687864b9fc464f8</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מתנאל סבח - שדרות דוממת</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409441&amp;sid=c5c30978038848a81687864b9fc464f8</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מני חן &amp; שום ראפר - שימי לב, מה ייתן לך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אורי זר - חוזר לילדות</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409440&amp;sid=c5c30978038848a81687864b9fc464f8</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אורי זר - חוזר לילדות</v>
+        <v>רפאל שילוני - מחכה לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב - חשבונות שמיים</v>
+        <v>נתנאל צ'אקי - ירח מלא</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409446&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409457&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב - חשבונות שמיים</v>
+        <v>נתנאל צ'אקי - ירח מלא</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רפאל שילוני - מחכה לך</v>
+        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409445&amp;sid=27f51e4d97173c14aa9eadc22e457f7c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409456&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,354 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רפאל שילוני - מחכה לך</v>
+        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נוי אגסי - בכל דרך שנלך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409455&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נוי אגסי - בכל דרך שנלך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מלי יקותיאל - כל היום</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409454&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מלי יקותיאל - כל היום</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאור יפרח - אל תאכזבי אותי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409453&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאור יפרח - אל תאכזבי אותי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יפתח גרינברג - כוכב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409452&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יפתח גרינברג - כוכב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יאנג בוטה - שוקי לעדן</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409451&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יאנג בוטה - שוקי לעדן</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409450&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>דניאל בן שימול - פתאום</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409449&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>דניאל בן שימול - פתאום</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>דורון מזר - מוזר להיות לבד</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409448&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>דורון מזר - מוזר להיות לבד</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אורן עדן - חייל של אמא</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409447&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אורן עדן - חייל של אמא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתנאל צ'אקי - ירח מלא</v>
+        <v>שמעון בוסקילה - מעליות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409457&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409460&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתנאל צ'אקי - ירח מלא</v>
+        <v>שמעון בוסקילה - מעליות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
+        <v>שיר אמלי - חיכיתי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409456&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409459&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-02</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ואנונו - לחיות איתך על הקצה</v>
+        <v>שיר אמלי - חיכיתי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוי אגסי - בכל דרך שנלך</v>
+        <v>שון בלו - אני בלו</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409455&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409458&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-02</v>
@@ -545,316 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוי אגסי - בכל דרך שנלך</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מלי יקותיאל - כל היום</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409454&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מלי יקותיאל - כל היום</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מאור יפרח - אל תאכזבי אותי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409453&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מאור יפרח - אל תאכזבי אותי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יפתח גרינברג - כוכב</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409452&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יפתח גרינברג - כוכב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>יאנג בוטה - שוקי לעדן</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409451&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>יאנג בוטה - שוקי לעדן</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409450&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>הרון הרון מארח את מנור שבת ופרחחי ירושלים - Every Time הורדה</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>דניאל בן שימול - פתאום</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409449&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>דניאל בן שימול - פתאום</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>דורון מזר - מוזר להיות לבד</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409448&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>דורון מזר - מוזר להיות לבד</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אורן עדן - חייל של אמא</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409447&amp;sid=b6567d7e27af4d463c6ac6d68f16ed82</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אורן עדן - חייל של אמא</v>
+        <v>שון בלו - אני בלו</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה - מעליות</v>
+        <v>בן אל תבורי - מי אני</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409460&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409479&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה - מעליות</v>
+        <v>בן אל תבורי - מי אני</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שיר אמלי - חיכיתי</v>
+        <v>אמיר ישראל - פוצי מוצי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409459&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409478&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שיר אמלי - חיכיתי</v>
+        <v>אמיר ישראל - פוצי מוצי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שון בלו - אני בלו</v>
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409458&amp;sid=596eb7a14186c6371d4797ff4f464372</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,7 +545,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שון בלו - אני בלו</v>
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן אל תבורי - מי אני</v>
+        <v>משה פרץ - ימים טובים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409479&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409483&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן אל תבורי - מי אני</v>
+        <v>משה פרץ - ימים טובים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אמיר ישראל - פוצי מוצי</v>
+        <v>חיים ציפל - תדליק לי נר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409478&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409482&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-04</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אמיר ישראל - פוצי מוצי</v>
+        <v>חיים ציפל - תדליק לי נר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
+        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=f25a1cf68326f713b4334e0bd420caa5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409481&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-04</v>
@@ -545,12 +545,50 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה</v>
+        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>דניאל כהן - למה פתאום חזרת</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409480&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>דניאל כהן - למה פתאום חזרת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה פרץ - ימים טובים</v>
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409483&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=81f569bfbe129aebcaf4b317ba1f5acf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה פרץ - ימים טובים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>חיים ציפל - תדליק לי נר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409482&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>חיים ציפל - תדליק לי נר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409481&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת - על אמת</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>דניאל כהן - למה פתאום חזרת</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409480&amp;sid=66852f0d514e2c5d13155a5d5d0f0788</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>דניאל כהן - למה פתאום חזרת</v>
+        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
+        <v>נדב חנציס - אהבה ראשונה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409477&amp;sid=81f569bfbe129aebcaf4b317ba1f5acf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409484&amp;sid=85c2be9d7b769a967dd94f06e90e8ff2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופק יפרח אזולאי - מה לי ולרומנטיקה קאבר</v>
+        <v>נדב חנציס - אהבה ראשונה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב חנציס - אהבה ראשונה</v>
+        <v>תמר כהנא - את הים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409484&amp;sid=85c2be9d7b769a967dd94f06e90e8ff2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409493&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב חנציס - אהבה ראשונה</v>
+        <v>תמר כהנא - את הים</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>תמר אופיר - שיר טיפול</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409491&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>תמר אופיר - שיר טיפול</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שירי מימון - חמצן</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409490&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שירי מימון - חמצן</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שילה אליה - אם הייתי יכול</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409489&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שילה אליה - אם הייתי יכול</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>שי שמואל פחימה - החיים</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409488&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>שי שמואל פחימה - החיים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>סטפן לגר - הלוך חזור</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409487&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>סטפן לגר - הלוך חזור</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נתי - תמיתי לי בלילה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409486&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נתי - תמיתי לי בלילה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>נדב חנציס - מפחד להתגבר עלייך</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409485&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>נדב חנציס - מפחד להתגבר עלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר כהנא - את הים</v>
+        <v>עדן חסון - חוזר לעצמי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409493&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409494&amp;sid=7f8aa5df0b2c0a2c1ebe6d5b5062b03c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר כהנא - את הים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>תמר אופיר - שיר טיפול</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409491&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>תמר אופיר - שיר טיפול</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שירי מימון - חמצן</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409490&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שירי מימון - חמצן</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שילה אליה - אם הייתי יכול</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409489&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שילה אליה - אם הייתי יכול</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>שי שמואל פחימה - החיים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409488&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>שי שמואל פחימה - החיים</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>סטפן לגר - הלוך חזור</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409487&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>סטפן לגר - הלוך חזור</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נתי - תמיתי לי בלילה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409486&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נתי - תמיתי לי בלילה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נדב חנציס - מפחד להתגבר עלייך</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409485&amp;sid=408464f7705d17e4fa184a3d6c479fa7</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נדב חנציס - מפחד להתגבר עלייך</v>
+        <v>עדן חסון - חוזר לעצמי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן חסון - חוזר לעצמי</v>
+        <v>רמי מור - הלב שלך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409494&amp;sid=7f8aa5df0b2c0a2c1ebe6d5b5062b03c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409510&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,582 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן חסון - חוזר לעצמי</v>
+        <v>רמי מור - הלב שלך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>קורין גמליאל - 2 בלילה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409509&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>קורין גמליאל - 2 בלילה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קארין אבלמן - מה לא ניצחנו</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409508&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קארין אבלמן - מה לא ניצחנו</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מרדכי בן ראובן - שמה הדסה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409507&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מרדכי בן ראובן - שמה הדסה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאי ספדיה - יותר מכולן</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409506&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאי ספדיה - יותר מכולן</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ליאור פינטו - תכף חורף</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409505&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>ליאור פינטו - תכף חורף</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>טל ורסנו - נופל מגעגוע</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409504&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>טל ורסנו - נופל מגעגוע</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>טונה - הייתי שם</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409503&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>טונה - הייתי שם</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>זהר מנור - אל תדאג</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409502&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>זהר מנור - אל תדאג</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>היוצרים - משתכרת מתירוש</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409501&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>היוצרים - משתכרת מתירוש</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>‎גלעד יחיא - חיבוק אחד קטן</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409500&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>‎גלעד יחיא - חיבוק אחד קטן</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אריאל אזולאי - היא שולטת בי</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409499&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אריאל אזולאי - היא שולטת בי</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>איתי לוי - בשעות הבודדות</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409498&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>איתי לוי - בשעות הבודדות</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אופיר חיים - צא אל החלום</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409497&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אופיר חיים - צא אל החלום</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אדיר ניזרי - בטוב וגם ברע בית"ר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409496&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אדיר ניזרי - בטוב וגם ברע בית"ר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אדיר יהודה - ריבונו של עולם</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409495&amp;sid=d9f34b05f44a6d478b86a88aad0ab3e6</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אדיר יהודה - ריבונו של עולם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
   </ignoredErrors>
 </worksheet>
 </file>